--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00845B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00845B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE7994AC-C90E-4EAA-A6C9-6E505F7464CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E2D0A97-1D58-4B88-B16F-06B72FBB78B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{D5A4CCF9-D2BE-415A-8A81-3BBE4225F5F1}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{E2E3A31E-632F-4073-9476-FE96CD428B80}"/>
   </bookViews>
   <sheets>
     <sheet name="00845B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1603,25 +1603,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18BC42D9-41B1-4A62-A6FB-268AE87622A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B3F32D1-12FB-4394-B50F-F718E437A9FC}">
   <dimension ref="A1:R40"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1649,7 +1649,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1679,7 +1679,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1775,7 +1775,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1829,7 +1829,7 @@
         <v>4.43</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1855,7 +1855,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2633,7 +2633,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2022</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2021</v>
       </c>
@@ -3077,7 +3077,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>27</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>27</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>27</v>
       </c>
@@ -3301,7 +3301,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2020</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>27</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>27</v>
       </c>
@@ -3467,7 +3467,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>27</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>27</v>
       </c>
@@ -3579,7 +3579,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="49">
         <v>2019</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>27</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="51" t="s">
         <v>72</v>
       </c>
